--- a/Data/CERP_PBC_WQ_Summary_Data.xlsx
+++ b/Data/CERP_PBC_WQ_Summary_Data.xlsx
@@ -6032,6 +6032,318 @@
         <v>6.31</v>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B41" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="C41" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="E41" t="n">
+        <v>5.34</v>
+      </c>
+      <c r="F41" t="n">
+        <v>5.53</v>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="H41" t="n">
+        <v>7.03</v>
+      </c>
+      <c r="I41" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="J41" t="n">
+        <v>6.93</v>
+      </c>
+      <c r="K41" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="L41" t="n">
+        <v>5.44</v>
+      </c>
+      <c r="M41" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="N41" t="n">
+        <v>7.03</v>
+      </c>
+      <c r="O41" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="P41" t="n">
+        <v>6.26</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>7.84</v>
+      </c>
+      <c r="R41" t="n">
+        <v>5.41</v>
+      </c>
+      <c r="S41" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="T41" t="n">
+        <v>5.79</v>
+      </c>
+      <c r="U41" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="V41" t="n">
+        <v>6</v>
+      </c>
+      <c r="W41" s="2" t="n">
+        <v>46205</v>
+      </c>
+      <c r="X41" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="AA41" s="2" t="n">
+        <v>46205</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>5.84</v>
+      </c>
+      <c r="AE41" s="2" t="n">
+        <v>46205</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>5.82</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>3.08</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>46245</v>
+      </c>
+      <c r="B42" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="C42" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>46245</v>
+      </c>
+      <c r="E42" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="F42" t="n">
+        <v>8.14</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>46238</v>
+      </c>
+      <c r="H42" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="I42" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="J42" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="K42" s="2" t="n">
+        <v>46238</v>
+      </c>
+      <c r="L42" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="M42" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="N42" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="O42" s="2" t="n">
+        <v>46238</v>
+      </c>
+      <c r="P42" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="S42" s="2" t="n">
+        <v>46238</v>
+      </c>
+      <c r="T42" t="n">
+        <v>6.66</v>
+      </c>
+      <c r="U42" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="V42" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W42" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="X42" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="AA42" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>8.36</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE42" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>6.97</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>4.46</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B43" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="C43" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="E43" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="F43" t="n">
+        <v>6.36</v>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="H43" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="I43" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="J43" t="n">
+        <v>7.65</v>
+      </c>
+      <c r="K43" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="L43" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="M43" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="N43" t="n">
+        <v>5.59</v>
+      </c>
+      <c r="O43" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="P43" t="n">
+        <v>5.61</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>6.71</v>
+      </c>
+      <c r="R43" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="S43" s="2" t="n">
+        <v>46268</v>
+      </c>
+      <c r="T43" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="U43" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="V43" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="W43" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="X43" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>6.39</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="AA43" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>7.47</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>5.96</v>
+      </c>
+      <c r="AE43" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>4.79</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>5.41</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -11531,6 +11843,417 @@
         <v>73.33</v>
       </c>
       <c r="AS40" t="n">
+        <v>83.33</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B41" t="n">
+        <v>100</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" t="n">
+        <v>100</v>
+      </c>
+      <c r="E41" t="n">
+        <v>100</v>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="G41" t="n">
+        <v>100</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
+        <v>100</v>
+      </c>
+      <c r="J41" t="n">
+        <v>100</v>
+      </c>
+      <c r="K41" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="L41" t="n">
+        <v>70</v>
+      </c>
+      <c r="M41" t="n">
+        <v>51.96</v>
+      </c>
+      <c r="N41" t="n">
+        <v>10</v>
+      </c>
+      <c r="O41" t="n">
+        <v>100</v>
+      </c>
+      <c r="P41" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>100</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" t="n">
+        <v>100</v>
+      </c>
+      <c r="T41" t="n">
+        <v>100</v>
+      </c>
+      <c r="U41" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="V41" t="n">
+        <v>100</v>
+      </c>
+      <c r="W41" t="n">
+        <v>0</v>
+      </c>
+      <c r="X41" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z41" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>100</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>100</v>
+      </c>
+      <c r="AE41" s="2" t="n">
+        <v>46205</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>100</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>100</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ41" s="2" t="n">
+        <v>46205</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>100</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>100</v>
+      </c>
+      <c r="AO41" s="2" t="n">
+        <v>46205</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>100</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>100</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>46245</v>
+      </c>
+      <c r="B42" t="n">
+        <v>100</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" t="n">
+        <v>100</v>
+      </c>
+      <c r="E42" t="n">
+        <v>100</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>46245</v>
+      </c>
+      <c r="G42" t="n">
+        <v>100</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>100</v>
+      </c>
+      <c r="J42" t="n">
+        <v>100</v>
+      </c>
+      <c r="K42" s="2" t="n">
+        <v>46238</v>
+      </c>
+      <c r="L42" t="n">
+        <v>100</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="n">
+        <v>100</v>
+      </c>
+      <c r="O42" t="n">
+        <v>100</v>
+      </c>
+      <c r="P42" s="2" t="n">
+        <v>46238</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>91.67</v>
+      </c>
+      <c r="R42" t="n">
+        <v>14.43</v>
+      </c>
+      <c r="S42" t="n">
+        <v>75</v>
+      </c>
+      <c r="T42" t="n">
+        <v>100</v>
+      </c>
+      <c r="U42" s="2" t="n">
+        <v>46238</v>
+      </c>
+      <c r="V42" t="n">
+        <v>100</v>
+      </c>
+      <c r="W42" t="n">
+        <v>0</v>
+      </c>
+      <c r="X42" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z42" s="2" t="n">
+        <v>46238</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>100</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>100</v>
+      </c>
+      <c r="AE42" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>100</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>100</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ42" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>100</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>100</v>
+      </c>
+      <c r="AO42" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>100</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>100</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B43" t="n">
+        <v>100</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" t="n">
+        <v>100</v>
+      </c>
+      <c r="E43" t="n">
+        <v>100</v>
+      </c>
+      <c r="F43" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="G43" t="n">
+        <v>100</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>100</v>
+      </c>
+      <c r="J43" t="n">
+        <v>100</v>
+      </c>
+      <c r="K43" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="L43" t="n">
+        <v>100</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="n">
+        <v>100</v>
+      </c>
+      <c r="O43" t="n">
+        <v>100</v>
+      </c>
+      <c r="P43" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>100</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" t="n">
+        <v>100</v>
+      </c>
+      <c r="T43" t="n">
+        <v>100</v>
+      </c>
+      <c r="U43" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="V43" t="n">
+        <v>100</v>
+      </c>
+      <c r="W43" t="n">
+        <v>0</v>
+      </c>
+      <c r="X43" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z43" s="2" t="n">
+        <v>46268</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>100</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>100</v>
+      </c>
+      <c r="AE43" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>90.48</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>16.49</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>71.43</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ43" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>100</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>100</v>
+      </c>
+      <c r="AO43" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="AP43" t="n">
+        <v>75.64</v>
+      </c>
+      <c r="AQ43" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AR43" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="AS43" t="n">
         <v>83.33</v>
       </c>
     </row>
@@ -15704,6 +16427,318 @@
         <v>29.3</v>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B41" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="C41" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="E41" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="F41" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="H41" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="I41" t="n">
+        <v>33</v>
+      </c>
+      <c r="J41" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="K41" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="L41" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="M41" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="N41" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="O41" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="P41" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="R41" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="S41" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="T41" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="U41" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="V41" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="W41" s="2" t="n">
+        <v>46205</v>
+      </c>
+      <c r="X41" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="AA41" s="2" t="n">
+        <v>46205</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="AE41" s="2" t="n">
+        <v>46205</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>31</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>31.3</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>46245</v>
+      </c>
+      <c r="B42" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="C42" t="n">
+        <v>31</v>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>46245</v>
+      </c>
+      <c r="E42" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="F42" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>46238</v>
+      </c>
+      <c r="H42" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="I42" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="J42" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="K42" s="2" t="n">
+        <v>46238</v>
+      </c>
+      <c r="L42" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="M42" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="N42" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="O42" s="2" t="n">
+        <v>46238</v>
+      </c>
+      <c r="P42" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>32</v>
+      </c>
+      <c r="R42" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="S42" s="2" t="n">
+        <v>46238</v>
+      </c>
+      <c r="T42" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="U42" t="n">
+        <v>32</v>
+      </c>
+      <c r="V42" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="W42" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="X42" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="AA42" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="AE42" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>30</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>30.7</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B43" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="C43" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="E43" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="F43" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="H43" t="n">
+        <v>31</v>
+      </c>
+      <c r="I43" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="J43" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="K43" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="L43" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="M43" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="N43" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="O43" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="P43" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>31</v>
+      </c>
+      <c r="R43" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="S43" s="2" t="n">
+        <v>46268</v>
+      </c>
+      <c r="T43" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="U43" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="V43" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="W43" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="X43" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="AA43" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="AE43" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>30.7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -21188,6 +22223,417 @@
       </c>
       <c r="AS40" t="n">
         <v>29.3</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B41" t="n">
+        <v>30.05</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="D41" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="E41" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="G41" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="I41" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="J41" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="K41" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="L41" t="n">
+        <v>32.93</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="N41" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="O41" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="P41" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="S41" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="T41" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="U41" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="V41" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="W41" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="X41" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="Z41" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>32.53</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="AE41" s="2" t="n">
+        <v>46205</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>30.83</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="AJ41" s="2" t="n">
+        <v>46205</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="AO41" s="2" t="n">
+        <v>46205</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>31.17</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>31</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>31.3</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>46245</v>
+      </c>
+      <c r="B42" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="D42" t="n">
+        <v>31</v>
+      </c>
+      <c r="E42" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>46245</v>
+      </c>
+      <c r="G42" t="n">
+        <v>31.45</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.07</v>
+      </c>
+      <c r="I42" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="J42" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="K42" s="2" t="n">
+        <v>46238</v>
+      </c>
+      <c r="L42" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="N42" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="O42" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="P42" s="2" t="n">
+        <v>46238</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>31.33</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="S42" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="T42" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="U42" s="2" t="n">
+        <v>46238</v>
+      </c>
+      <c r="V42" t="n">
+        <v>31.77</v>
+      </c>
+      <c r="W42" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="X42" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>32</v>
+      </c>
+      <c r="Z42" s="2" t="n">
+        <v>46238</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>31.83</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>32</v>
+      </c>
+      <c r="AE42" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>29.43</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="AJ42" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>29.43</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="AO42" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>0.56</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>30.7</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B43" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="D43" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="E43" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="F43" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="G43" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="I43" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="J43" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="K43" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="L43" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N43" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="O43" t="n">
+        <v>31</v>
+      </c>
+      <c r="P43" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>31</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="S43" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="T43" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="U43" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="V43" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="W43" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="X43" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>31</v>
+      </c>
+      <c r="Z43" s="2" t="n">
+        <v>46268</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>29.47</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="AE43" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>29.67</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="AJ43" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>29.77</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="AO43" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="AP43" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="AQ43" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AR43" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>30.7</v>
       </c>
     </row>
   </sheetData>
@@ -26692,6 +28138,417 @@
         <v>8.27</v>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B41" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="D41" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="E41" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="G41" t="n">
+        <v>5.44</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="I41" t="n">
+        <v>5.34</v>
+      </c>
+      <c r="J41" t="n">
+        <v>5.53</v>
+      </c>
+      <c r="K41" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="L41" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="N41" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="O41" t="n">
+        <v>7.03</v>
+      </c>
+      <c r="P41" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5.44</v>
+      </c>
+      <c r="T41" t="n">
+        <v>7.03</v>
+      </c>
+      <c r="U41" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="V41" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X41" t="n">
+        <v>5.41</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>7.84</v>
+      </c>
+      <c r="Z41" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>5.79</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="AE41" s="2" t="n">
+        <v>46205</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="AJ41" s="2" t="n">
+        <v>46205</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="AO41" s="2" t="n">
+        <v>46205</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>46245</v>
+      </c>
+      <c r="B42" t="n">
+        <v>5.03</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="D42" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="E42" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>46245</v>
+      </c>
+      <c r="G42" t="n">
+        <v>6.93</v>
+      </c>
+      <c r="H42" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="I42" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="J42" t="n">
+        <v>8.14</v>
+      </c>
+      <c r="K42" s="2" t="n">
+        <v>46238</v>
+      </c>
+      <c r="L42" t="n">
+        <v>5.19</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0.69</v>
+      </c>
+      <c r="N42" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="O42" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="P42" s="2" t="n">
+        <v>46238</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="S42" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="T42" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="U42" s="2" t="n">
+        <v>46238</v>
+      </c>
+      <c r="V42" t="n">
+        <v>6.38</v>
+      </c>
+      <c r="W42" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="X42" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="Z42" s="2" t="n">
+        <v>46238</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>7.34</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>6.66</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="AE42" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="AJ42" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>6.37</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>8.36</v>
+      </c>
+      <c r="AO42" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>5.46</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>6.97</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B43" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="C43" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="D43" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="E43" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="F43" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="G43" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="I43" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="J43" t="n">
+        <v>6.36</v>
+      </c>
+      <c r="K43" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="L43" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="M43" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="N43" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="O43" t="n">
+        <v>7.65</v>
+      </c>
+      <c r="P43" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="S43" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="T43" t="n">
+        <v>5.59</v>
+      </c>
+      <c r="U43" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="V43" t="n">
+        <v>5.73</v>
+      </c>
+      <c r="W43" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="X43" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>6.71</v>
+      </c>
+      <c r="Z43" s="2" t="n">
+        <v>46268</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="AE43" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>5.76</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>6.39</v>
+      </c>
+      <c r="AJ43" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>7.47</v>
+      </c>
+      <c r="AO43" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="AP43" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="AQ43" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AR43" t="n">
+        <v>4.79</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>5.41</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -30872,6 +32729,318 @@
       </c>
       <c r="AH40" t="n">
         <v>80.3</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B41" t="n">
+        <v>69.4</v>
+      </c>
+      <c r="C41" t="n">
+        <v>81</v>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="E41" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="F41" t="n">
+        <v>90</v>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="H41" t="n">
+        <v>117.3</v>
+      </c>
+      <c r="I41" t="n">
+        <v>89.8</v>
+      </c>
+      <c r="J41" t="n">
+        <v>116.5</v>
+      </c>
+      <c r="K41" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="L41" t="n">
+        <v>91.1</v>
+      </c>
+      <c r="M41" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="N41" t="n">
+        <v>117.7</v>
+      </c>
+      <c r="O41" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="P41" t="n">
+        <v>98.1</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>127.6</v>
+      </c>
+      <c r="R41" t="n">
+        <v>82.4</v>
+      </c>
+      <c r="S41" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="T41" t="n">
+        <v>94.9</v>
+      </c>
+      <c r="U41" t="n">
+        <v>128.8</v>
+      </c>
+      <c r="V41" t="n">
+        <v>97.2</v>
+      </c>
+      <c r="W41" s="2" t="n">
+        <v>46205</v>
+      </c>
+      <c r="X41" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>73.4</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>70.9</v>
+      </c>
+      <c r="AA41" s="2" t="n">
+        <v>46205</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>97.4</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>84.6</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>85.6</v>
+      </c>
+      <c r="AE41" s="2" t="n">
+        <v>46205</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>91</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>86.9</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>45.5</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>46245</v>
+      </c>
+      <c r="B42" t="n">
+        <v>81.1</v>
+      </c>
+      <c r="C42" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>46245</v>
+      </c>
+      <c r="E42" t="n">
+        <v>91.6</v>
+      </c>
+      <c r="F42" t="n">
+        <v>134.8</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>46238</v>
+      </c>
+      <c r="H42" t="n">
+        <v>76.1</v>
+      </c>
+      <c r="I42" t="n">
+        <v>77.2</v>
+      </c>
+      <c r="J42" t="n">
+        <v>97.8</v>
+      </c>
+      <c r="K42" s="2" t="n">
+        <v>46238</v>
+      </c>
+      <c r="L42" t="n">
+        <v>81.4</v>
+      </c>
+      <c r="M42" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="N42" t="n">
+        <v>85.2</v>
+      </c>
+      <c r="O42" s="2" t="n">
+        <v>46238</v>
+      </c>
+      <c r="P42" t="n">
+        <v>97.6</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>107.7</v>
+      </c>
+      <c r="R42" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="S42" s="2" t="n">
+        <v>46238</v>
+      </c>
+      <c r="T42" t="n">
+        <v>106.7</v>
+      </c>
+      <c r="U42" t="n">
+        <v>127.3</v>
+      </c>
+      <c r="V42" t="n">
+        <v>121.5</v>
+      </c>
+      <c r="W42" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="X42" t="n">
+        <v>61.1</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>71.6</v>
+      </c>
+      <c r="AA42" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>65.7</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>118.4</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>84.5</v>
+      </c>
+      <c r="AE42" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>64.4</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B43" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="C43" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="E43" t="n">
+        <v>85.3</v>
+      </c>
+      <c r="F43" t="n">
+        <v>107.5</v>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="H43" t="n">
+        <v>80.2</v>
+      </c>
+      <c r="I43" t="n">
+        <v>69</v>
+      </c>
+      <c r="J43" t="n">
+        <v>123.6</v>
+      </c>
+      <c r="K43" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="L43" t="n">
+        <v>75.1</v>
+      </c>
+      <c r="M43" t="n">
+        <v>80.7</v>
+      </c>
+      <c r="N43" t="n">
+        <v>90.7</v>
+      </c>
+      <c r="O43" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="P43" t="n">
+        <v>82.7</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>99</v>
+      </c>
+      <c r="R43" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="S43" s="2" t="n">
+        <v>46268</v>
+      </c>
+      <c r="T43" t="n">
+        <v>57.9</v>
+      </c>
+      <c r="U43" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="V43" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="W43" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="X43" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>92</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="AA43" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>76.4</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>82.9</v>
+      </c>
+      <c r="AE43" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>71.7</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>69.1</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>75.9</v>
       </c>
     </row>
   </sheetData>
@@ -36469,6 +38638,417 @@
         <v>119</v>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B41" t="n">
+        <v>75.2</v>
+      </c>
+      <c r="C41" t="n">
+        <v>8.2</v>
+      </c>
+      <c r="D41" t="n">
+        <v>69.4</v>
+      </c>
+      <c r="E41" t="n">
+        <v>81</v>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="G41" t="n">
+        <v>87.85</v>
+      </c>
+      <c r="H41" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="I41" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="J41" t="n">
+        <v>90</v>
+      </c>
+      <c r="K41" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="L41" t="n">
+        <v>107.87</v>
+      </c>
+      <c r="M41" t="n">
+        <v>15.65</v>
+      </c>
+      <c r="N41" t="n">
+        <v>89.8</v>
+      </c>
+      <c r="O41" t="n">
+        <v>117.3</v>
+      </c>
+      <c r="P41" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>102.67</v>
+      </c>
+      <c r="R41" t="n">
+        <v>13.63</v>
+      </c>
+      <c r="S41" t="n">
+        <v>91.1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>117.7</v>
+      </c>
+      <c r="U41" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="V41" t="n">
+        <v>102.7</v>
+      </c>
+      <c r="W41" t="n">
+        <v>22.95</v>
+      </c>
+      <c r="X41" t="n">
+        <v>82.4</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>127.6</v>
+      </c>
+      <c r="Z41" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>106.97</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>18.94</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>94.9</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>128.8</v>
+      </c>
+      <c r="AE41" s="2" t="n">
+        <v>46205</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>72.6</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>70.9</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="AJ41" s="2" t="n">
+        <v>46205</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>89.2</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>7.12</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>84.6</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>97.4</v>
+      </c>
+      <c r="AO41" s="2" t="n">
+        <v>46205</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>74.47</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>25.17</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>46245</v>
+      </c>
+      <c r="B42" t="n">
+        <v>77.45</v>
+      </c>
+      <c r="C42" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="D42" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="E42" t="n">
+        <v>81.1</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>46245</v>
+      </c>
+      <c r="G42" t="n">
+        <v>113.2</v>
+      </c>
+      <c r="H42" t="n">
+        <v>30.55</v>
+      </c>
+      <c r="I42" t="n">
+        <v>91.6</v>
+      </c>
+      <c r="J42" t="n">
+        <v>134.8</v>
+      </c>
+      <c r="K42" s="2" t="n">
+        <v>46238</v>
+      </c>
+      <c r="L42" t="n">
+        <v>83.7</v>
+      </c>
+      <c r="M42" t="n">
+        <v>12.22</v>
+      </c>
+      <c r="N42" t="n">
+        <v>76.1</v>
+      </c>
+      <c r="O42" t="n">
+        <v>97.8</v>
+      </c>
+      <c r="P42" s="2" t="n">
+        <v>46238</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>79.93</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6.13</v>
+      </c>
+      <c r="S42" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="T42" t="n">
+        <v>85.2</v>
+      </c>
+      <c r="U42" s="2" t="n">
+        <v>46238</v>
+      </c>
+      <c r="V42" t="n">
+        <v>100.37</v>
+      </c>
+      <c r="W42" t="n">
+        <v>6.41</v>
+      </c>
+      <c r="X42" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>107.7</v>
+      </c>
+      <c r="Z42" s="2" t="n">
+        <v>46238</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>118.5</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>10.62</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>106.7</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>127.3</v>
+      </c>
+      <c r="AE42" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>66.3</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>61.1</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>71.6</v>
+      </c>
+      <c r="AJ42" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>89.53</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>26.71</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>65.7</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>118.4</v>
+      </c>
+      <c r="AO42" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>78.27</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>18.83</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>64.4</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>99.7</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B43" t="n">
+        <v>83.1</v>
+      </c>
+      <c r="C43" t="n">
+        <v>17.54</v>
+      </c>
+      <c r="D43" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="E43" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="F43" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="G43" t="n">
+        <v>96.4</v>
+      </c>
+      <c r="H43" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="I43" t="n">
+        <v>85.3</v>
+      </c>
+      <c r="J43" t="n">
+        <v>107.5</v>
+      </c>
+      <c r="K43" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="L43" t="n">
+        <v>90.93</v>
+      </c>
+      <c r="M43" t="n">
+        <v>28.84</v>
+      </c>
+      <c r="N43" t="n">
+        <v>69</v>
+      </c>
+      <c r="O43" t="n">
+        <v>123.6</v>
+      </c>
+      <c r="P43" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>82.17</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="S43" t="n">
+        <v>75.1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>90.7</v>
+      </c>
+      <c r="U43" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="V43" t="n">
+        <v>83.83</v>
+      </c>
+      <c r="W43" t="n">
+        <v>14.63</v>
+      </c>
+      <c r="X43" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>99</v>
+      </c>
+      <c r="Z43" s="2" t="n">
+        <v>46268</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>63.07</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>9.92</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="AE43" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>83</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>9.43</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>92</v>
+      </c>
+      <c r="AJ43" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>87.9</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>14.65</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>76.4</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="AO43" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="AP43" t="n">
+        <v>72.23</v>
+      </c>
+      <c r="AQ43" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="AR43" t="n">
+        <v>69.1</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>75.9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -40484,6 +43064,318 @@
       </c>
       <c r="AH40" t="n">
         <v>7.86</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B41" t="n">
+        <v>7.64</v>
+      </c>
+      <c r="C41" t="n">
+        <v>7.78</v>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="E41" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="F41" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="H41" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="I41" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="J41" t="n">
+        <v>7.97</v>
+      </c>
+      <c r="K41" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="L41" t="n">
+        <v>7.86</v>
+      </c>
+      <c r="M41" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="N41" t="n">
+        <v>7.81</v>
+      </c>
+      <c r="O41" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="P41" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>8.03</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7.79</v>
+      </c>
+      <c r="S41" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="T41" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="U41" t="n">
+        <v>8.03</v>
+      </c>
+      <c r="V41" t="n">
+        <v>7.86</v>
+      </c>
+      <c r="W41" s="2" t="n">
+        <v>46205</v>
+      </c>
+      <c r="X41" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AA41" s="2" t="n">
+        <v>46205</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>7.95</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>7.87</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>7.86</v>
+      </c>
+      <c r="AE41" s="2" t="n">
+        <v>46205</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>7.86</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>46245</v>
+      </c>
+      <c r="B42" t="n">
+        <v>7.74</v>
+      </c>
+      <c r="C42" t="n">
+        <v>7.77</v>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>46245</v>
+      </c>
+      <c r="E42" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="F42" t="n">
+        <v>8.08</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>46238</v>
+      </c>
+      <c r="H42" t="n">
+        <v>7.62</v>
+      </c>
+      <c r="I42" t="n">
+        <v>7.59</v>
+      </c>
+      <c r="J42" t="n">
+        <v>7.81</v>
+      </c>
+      <c r="K42" s="2" t="n">
+        <v>46238</v>
+      </c>
+      <c r="L42" t="n">
+        <v>7.65</v>
+      </c>
+      <c r="M42" t="n">
+        <v>7.52</v>
+      </c>
+      <c r="N42" t="n">
+        <v>7.68</v>
+      </c>
+      <c r="O42" s="2" t="n">
+        <v>46238</v>
+      </c>
+      <c r="P42" t="n">
+        <v>7.77</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>7.84</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7.77</v>
+      </c>
+      <c r="S42" s="2" t="n">
+        <v>46238</v>
+      </c>
+      <c r="T42" t="n">
+        <v>7.87</v>
+      </c>
+      <c r="U42" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="V42" t="n">
+        <v>7.89</v>
+      </c>
+      <c r="W42" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="X42" t="n">
+        <v>7.69</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>7.68</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>7.71</v>
+      </c>
+      <c r="AA42" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>7.67</v>
+      </c>
+      <c r="AE42" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>7.84</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>7.62</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B43" t="n">
+        <v>7.71</v>
+      </c>
+      <c r="C43" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="E43" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="F43" t="n">
+        <v>8</v>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="H43" t="n">
+        <v>7.71</v>
+      </c>
+      <c r="I43" t="n">
+        <v>7.61</v>
+      </c>
+      <c r="J43" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="K43" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="L43" t="n">
+        <v>7.67</v>
+      </c>
+      <c r="M43" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="N43" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="O43" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="P43" t="n">
+        <v>7.72</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>7.78</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7.57</v>
+      </c>
+      <c r="S43" s="2" t="n">
+        <v>46268</v>
+      </c>
+      <c r="T43" t="n">
+        <v>7.59</v>
+      </c>
+      <c r="U43" t="n">
+        <v>7.68</v>
+      </c>
+      <c r="V43" t="n">
+        <v>7.69</v>
+      </c>
+      <c r="W43" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="X43" t="n">
+        <v>7.81</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>7.69</v>
+      </c>
+      <c r="AA43" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>7.49</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>7.95</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>7.73</v>
+      </c>
+      <c r="AE43" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>7.88</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>7.61</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>7.55</v>
       </c>
     </row>
   </sheetData>
@@ -45799,6 +48691,417 @@
         <v>8.1199999999999992</v>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B41" t="n">
+        <v>7.71</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D41" t="n">
+        <v>7.64</v>
+      </c>
+      <c r="E41" t="n">
+        <v>7.78</v>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="G41" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I41" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="J41" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="K41" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="L41" t="n">
+        <v>7.89</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="N41" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="O41" t="n">
+        <v>7.97</v>
+      </c>
+      <c r="P41" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>7.86</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="S41" t="n">
+        <v>7.81</v>
+      </c>
+      <c r="T41" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="U41" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="V41" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="W41" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="X41" t="n">
+        <v>7.79</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>8.03</v>
+      </c>
+      <c r="Z41" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>7.93</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>7.86</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>8.03</v>
+      </c>
+      <c r="AE41" s="2" t="n">
+        <v>46205</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="AJ41" s="2" t="n">
+        <v>46205</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>7.89</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>7.86</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>7.95</v>
+      </c>
+      <c r="AO41" s="2" t="n">
+        <v>46205</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>7.9</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>46245</v>
+      </c>
+      <c r="B42" t="n">
+        <v>7.76</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D42" t="n">
+        <v>7.74</v>
+      </c>
+      <c r="E42" t="n">
+        <v>7.77</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>46245</v>
+      </c>
+      <c r="G42" t="n">
+        <v>8</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I42" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="J42" t="n">
+        <v>8.08</v>
+      </c>
+      <c r="K42" s="2" t="n">
+        <v>46238</v>
+      </c>
+      <c r="L42" t="n">
+        <v>7.67</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N42" t="n">
+        <v>7.59</v>
+      </c>
+      <c r="O42" t="n">
+        <v>7.81</v>
+      </c>
+      <c r="P42" s="2" t="n">
+        <v>46238</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>7.62</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="S42" t="n">
+        <v>7.52</v>
+      </c>
+      <c r="T42" t="n">
+        <v>7.68</v>
+      </c>
+      <c r="U42" s="2" t="n">
+        <v>46238</v>
+      </c>
+      <c r="V42" t="n">
+        <v>7.79</v>
+      </c>
+      <c r="W42" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="X42" t="n">
+        <v>7.77</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>7.84</v>
+      </c>
+      <c r="Z42" s="2" t="n">
+        <v>46238</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>7.89</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>7.87</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="AE42" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>7.69</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>7.68</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>7.71</v>
+      </c>
+      <c r="AJ42" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>7.68</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="AO42" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>7.65</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>7.84</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B43" t="n">
+        <v>7.81</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D43" t="n">
+        <v>7.71</v>
+      </c>
+      <c r="E43" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="F43" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="G43" t="n">
+        <v>7.97</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="I43" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="J43" t="n">
+        <v>8</v>
+      </c>
+      <c r="K43" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="L43" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="N43" t="n">
+        <v>7.61</v>
+      </c>
+      <c r="O43" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="P43" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>7.69</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="S43" t="n">
+        <v>7.67</v>
+      </c>
+      <c r="T43" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="U43" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="V43" t="n">
+        <v>7.69</v>
+      </c>
+      <c r="W43" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="X43" t="n">
+        <v>7.57</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>7.78</v>
+      </c>
+      <c r="Z43" s="2" t="n">
+        <v>46268</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>7.65</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>7.59</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>7.69</v>
+      </c>
+      <c r="AE43" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>7.78</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>7.69</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="AJ43" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>7.72</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>7.49</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>7.95</v>
+      </c>
+      <c r="AO43" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="AP43" t="n">
+        <v>7.68</v>
+      </c>
+      <c r="AQ43" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AR43" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>7.88</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -49979,6 +53282,318 @@
       </c>
       <c r="AH40" t="n">
         <v>13.93</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B41" t="n">
+        <v>25.57</v>
+      </c>
+      <c r="C41" t="n">
+        <v>27.27</v>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="E41" t="n">
+        <v>34.64</v>
+      </c>
+      <c r="F41" t="n">
+        <v>36.19</v>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="H41" t="n">
+        <v>34.03</v>
+      </c>
+      <c r="I41" t="n">
+        <v>34.01</v>
+      </c>
+      <c r="J41" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="K41" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="L41" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="M41" t="n">
+        <v>34.34</v>
+      </c>
+      <c r="N41" t="n">
+        <v>33.86</v>
+      </c>
+      <c r="O41" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="P41" t="n">
+        <v>21.33</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="R41" t="n">
+        <v>16.34</v>
+      </c>
+      <c r="S41" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="T41" t="n">
+        <v>31.09</v>
+      </c>
+      <c r="U41" t="n">
+        <v>30.63</v>
+      </c>
+      <c r="V41" t="n">
+        <v>29.63</v>
+      </c>
+      <c r="W41" s="2" t="n">
+        <v>46205</v>
+      </c>
+      <c r="X41" t="n">
+        <v>22.99</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>21.85</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>21.29</v>
+      </c>
+      <c r="AA41" s="2" t="n">
+        <v>46205</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>16.41</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>17.99</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>16.79</v>
+      </c>
+      <c r="AE41" s="2" t="n">
+        <v>46205</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>18.92</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>19.37</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>16.06</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>46245</v>
+      </c>
+      <c r="B42" t="n">
+        <v>21.93</v>
+      </c>
+      <c r="C42" t="n">
+        <v>23.89</v>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>46245</v>
+      </c>
+      <c r="E42" t="n">
+        <v>31.02</v>
+      </c>
+      <c r="F42" t="n">
+        <v>35.46</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>46238</v>
+      </c>
+      <c r="H42" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="I42" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="J42" t="n">
+        <v>34.75</v>
+      </c>
+      <c r="K42" s="2" t="n">
+        <v>46238</v>
+      </c>
+      <c r="L42" t="n">
+        <v>32.43</v>
+      </c>
+      <c r="M42" t="n">
+        <v>33.42</v>
+      </c>
+      <c r="N42" t="n">
+        <v>33.46</v>
+      </c>
+      <c r="O42" s="2" t="n">
+        <v>46238</v>
+      </c>
+      <c r="P42" t="n">
+        <v>26.48</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>27.07</v>
+      </c>
+      <c r="R42" t="n">
+        <v>25.99</v>
+      </c>
+      <c r="S42" s="2" t="n">
+        <v>46238</v>
+      </c>
+      <c r="T42" t="n">
+        <v>30.09</v>
+      </c>
+      <c r="U42" t="n">
+        <v>30.64</v>
+      </c>
+      <c r="V42" t="n">
+        <v>31.27</v>
+      </c>
+      <c r="W42" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="X42" t="n">
+        <v>20.34</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>18.87</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>16.59</v>
+      </c>
+      <c r="AA42" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>13.89</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="AE42" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>15.33</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>15.98</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B43" t="n">
+        <v>15.24</v>
+      </c>
+      <c r="C43" t="n">
+        <v>17.61</v>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="E43" t="n">
+        <v>28.06</v>
+      </c>
+      <c r="F43" t="n">
+        <v>29.75</v>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="H43" t="n">
+        <v>32.84</v>
+      </c>
+      <c r="I43" t="n">
+        <v>31.82</v>
+      </c>
+      <c r="J43" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="K43" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="L43" t="n">
+        <v>32.54</v>
+      </c>
+      <c r="M43" t="n">
+        <v>32.37</v>
+      </c>
+      <c r="N43" t="n">
+        <v>33.57</v>
+      </c>
+      <c r="O43" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="P43" t="n">
+        <v>18.34</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>16.84</v>
+      </c>
+      <c r="R43" t="n">
+        <v>13.39</v>
+      </c>
+      <c r="S43" s="2" t="n">
+        <v>46268</v>
+      </c>
+      <c r="T43" t="n">
+        <v>24.98</v>
+      </c>
+      <c r="U43" t="n">
+        <v>24.26</v>
+      </c>
+      <c r="V43" t="n">
+        <v>28.02</v>
+      </c>
+      <c r="W43" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="X43" t="n">
+        <v>20.51</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>15.45</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>13.83</v>
+      </c>
+      <c r="AA43" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>10.38</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>10.83</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>9.63</v>
+      </c>
+      <c r="AE43" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>15.08</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>12.02</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>8.88</v>
       </c>
     </row>
   </sheetData>
@@ -55483,6 +59098,417 @@
         <v>17.2</v>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B41" t="n">
+        <v>26.42</v>
+      </c>
+      <c r="C41" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D41" t="n">
+        <v>25.57</v>
+      </c>
+      <c r="E41" t="n">
+        <v>27.27</v>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="G41" t="n">
+        <v>35.42</v>
+      </c>
+      <c r="H41" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I41" t="n">
+        <v>34.64</v>
+      </c>
+      <c r="J41" t="n">
+        <v>36.19</v>
+      </c>
+      <c r="K41" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="L41" t="n">
+        <v>34.34</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0.56</v>
+      </c>
+      <c r="N41" t="n">
+        <v>34.01</v>
+      </c>
+      <c r="O41" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="P41" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="S41" t="n">
+        <v>33.86</v>
+      </c>
+      <c r="T41" t="n">
+        <v>34.34</v>
+      </c>
+      <c r="U41" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="V41" t="n">
+        <v>20.76</v>
+      </c>
+      <c r="W41" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="X41" t="n">
+        <v>16.34</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="Z41" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>30.45</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>29.63</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>31.09</v>
+      </c>
+      <c r="AE41" s="2" t="n">
+        <v>46205</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>22.04</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>21.29</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>22.99</v>
+      </c>
+      <c r="AJ41" s="2" t="n">
+        <v>46205</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>17.06</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>16.41</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>17.99</v>
+      </c>
+      <c r="AO41" s="2" t="n">
+        <v>46205</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>18.12</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>16.06</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>19.37</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>46245</v>
+      </c>
+      <c r="B42" t="n">
+        <v>22.91</v>
+      </c>
+      <c r="C42" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="D42" t="n">
+        <v>21.93</v>
+      </c>
+      <c r="E42" t="n">
+        <v>23.89</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>46245</v>
+      </c>
+      <c r="G42" t="n">
+        <v>33.24</v>
+      </c>
+      <c r="H42" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="I42" t="n">
+        <v>31.02</v>
+      </c>
+      <c r="J42" t="n">
+        <v>35.46</v>
+      </c>
+      <c r="K42" s="2" t="n">
+        <v>46238</v>
+      </c>
+      <c r="L42" t="n">
+        <v>32.65</v>
+      </c>
+      <c r="M42" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="N42" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="O42" t="n">
+        <v>34.75</v>
+      </c>
+      <c r="P42" s="2" t="n">
+        <v>46238</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="S42" t="n">
+        <v>32.43</v>
+      </c>
+      <c r="T42" t="n">
+        <v>33.46</v>
+      </c>
+      <c r="U42" s="2" t="n">
+        <v>46238</v>
+      </c>
+      <c r="V42" t="n">
+        <v>26.51</v>
+      </c>
+      <c r="W42" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="X42" t="n">
+        <v>25.99</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>27.07</v>
+      </c>
+      <c r="Z42" s="2" t="n">
+        <v>46238</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>30.67</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>30.09</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>31.27</v>
+      </c>
+      <c r="AE42" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>16.59</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>20.34</v>
+      </c>
+      <c r="AJ42" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>12.91</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>13.89</v>
+      </c>
+      <c r="AO42" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>15.24</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>15.98</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B43" t="n">
+        <v>16.42</v>
+      </c>
+      <c r="C43" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="D43" t="n">
+        <v>15.24</v>
+      </c>
+      <c r="E43" t="n">
+        <v>17.61</v>
+      </c>
+      <c r="F43" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="G43" t="n">
+        <v>28.91</v>
+      </c>
+      <c r="H43" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I43" t="n">
+        <v>28.06</v>
+      </c>
+      <c r="J43" t="n">
+        <v>29.75</v>
+      </c>
+      <c r="K43" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="L43" t="n">
+        <v>32.82</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="N43" t="n">
+        <v>31.82</v>
+      </c>
+      <c r="O43" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="P43" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>32.83</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="S43" t="n">
+        <v>32.37</v>
+      </c>
+      <c r="T43" t="n">
+        <v>33.57</v>
+      </c>
+      <c r="U43" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="V43" t="n">
+        <v>16.19</v>
+      </c>
+      <c r="W43" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="X43" t="n">
+        <v>13.39</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>18.34</v>
+      </c>
+      <c r="Z43" s="2" t="n">
+        <v>46268</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>25.75</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>24.26</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>28.02</v>
+      </c>
+      <c r="AE43" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>13.83</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>20.51</v>
+      </c>
+      <c r="AJ43" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>10.28</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>9.63</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>10.83</v>
+      </c>
+      <c r="AO43" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="AP43" t="n">
+        <v>11.99</v>
+      </c>
+      <c r="AQ43" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AR43" t="n">
+        <v>8.88</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>15.08</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -59663,6 +63689,318 @@
         <v>73.33</v>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B41" t="n">
+        <v>100</v>
+      </c>
+      <c r="C41" t="n">
+        <v>100</v>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="E41" t="n">
+        <v>100</v>
+      </c>
+      <c r="F41" t="n">
+        <v>100</v>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="H41" t="n">
+        <v>100</v>
+      </c>
+      <c r="I41" t="n">
+        <v>100</v>
+      </c>
+      <c r="J41" t="n">
+        <v>10</v>
+      </c>
+      <c r="K41" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="L41" t="n">
+        <v>100</v>
+      </c>
+      <c r="M41" t="n">
+        <v>100</v>
+      </c>
+      <c r="N41" t="n">
+        <v>100</v>
+      </c>
+      <c r="O41" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="P41" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>100</v>
+      </c>
+      <c r="R41" t="n">
+        <v>100</v>
+      </c>
+      <c r="S41" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="T41" t="n">
+        <v>100</v>
+      </c>
+      <c r="U41" t="n">
+        <v>100</v>
+      </c>
+      <c r="V41" t="n">
+        <v>100</v>
+      </c>
+      <c r="W41" s="2" t="n">
+        <v>46205</v>
+      </c>
+      <c r="X41" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA41" s="2" t="n">
+        <v>46205</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>100</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>100</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>100</v>
+      </c>
+      <c r="AE41" s="2" t="n">
+        <v>46205</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>100</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>46245</v>
+      </c>
+      <c r="B42" t="n">
+        <v>100</v>
+      </c>
+      <c r="C42" t="n">
+        <v>100</v>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>46245</v>
+      </c>
+      <c r="E42" t="n">
+        <v>100</v>
+      </c>
+      <c r="F42" t="n">
+        <v>100</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>46238</v>
+      </c>
+      <c r="H42" t="n">
+        <v>100</v>
+      </c>
+      <c r="I42" t="n">
+        <v>100</v>
+      </c>
+      <c r="J42" t="n">
+        <v>100</v>
+      </c>
+      <c r="K42" s="2" t="n">
+        <v>46238</v>
+      </c>
+      <c r="L42" t="n">
+        <v>75</v>
+      </c>
+      <c r="M42" t="n">
+        <v>100</v>
+      </c>
+      <c r="N42" t="n">
+        <v>100</v>
+      </c>
+      <c r="O42" s="2" t="n">
+        <v>46238</v>
+      </c>
+      <c r="P42" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>100</v>
+      </c>
+      <c r="R42" t="n">
+        <v>100</v>
+      </c>
+      <c r="S42" s="2" t="n">
+        <v>46238</v>
+      </c>
+      <c r="T42" t="n">
+        <v>100</v>
+      </c>
+      <c r="U42" t="n">
+        <v>100</v>
+      </c>
+      <c r="V42" t="n">
+        <v>100</v>
+      </c>
+      <c r="W42" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="X42" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA42" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>100</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>100</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>100</v>
+      </c>
+      <c r="AE42" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>100</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B43" t="n">
+        <v>100</v>
+      </c>
+      <c r="C43" t="n">
+        <v>100</v>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="E43" t="n">
+        <v>100</v>
+      </c>
+      <c r="F43" t="n">
+        <v>100</v>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="H43" t="n">
+        <v>100</v>
+      </c>
+      <c r="I43" t="n">
+        <v>100</v>
+      </c>
+      <c r="J43" t="n">
+        <v>100</v>
+      </c>
+      <c r="K43" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="L43" t="n">
+        <v>100</v>
+      </c>
+      <c r="M43" t="n">
+        <v>100</v>
+      </c>
+      <c r="N43" t="n">
+        <v>100</v>
+      </c>
+      <c r="O43" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="P43" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>100</v>
+      </c>
+      <c r="R43" t="n">
+        <v>100</v>
+      </c>
+      <c r="S43" s="2" t="n">
+        <v>46268</v>
+      </c>
+      <c r="T43" t="n">
+        <v>100</v>
+      </c>
+      <c r="U43" t="n">
+        <v>100</v>
+      </c>
+      <c r="V43" t="n">
+        <v>100</v>
+      </c>
+      <c r="W43" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="X43" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>71.43</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA43" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>100</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>100</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>100</v>
+      </c>
+      <c r="AE43" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>83.33</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>76.92</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
